--- a/data/trans_dic/P16A_n_R3-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A_n_R3-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,1</t>
+          <t>0,61; 3,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,09</t>
+          <t>0,23; 2,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,46</t>
+          <t>0,7; 3,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,04</t>
+          <t>1,6; 4,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,85</t>
+          <t>0,64; 3,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,65</t>
+          <t>0,99; 5,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,38</t>
+          <t>0,6; 3,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,26; 6,68</t>
+          <t>3,18; 6,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,8</t>
+          <t>0,91; 2,85</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,21</t>
+          <t>0,8; 2,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,69</t>
+          <t>0,79; 2,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 4,84</t>
+          <t>2,71; 4,73</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,95</t>
+          <t>0,22; 2,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,48</t>
+          <t>0,77; 4,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,67</t>
+          <t>3,06; 6,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,5</t>
+          <t>1,17; 4,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,34</t>
+          <t>0,77; 3,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 7,38</t>
+          <t>3,9; 7,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,4</t>
+          <t>0,24; 1,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,57</t>
+          <t>1,1; 3,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,11</t>
+          <t>0,4; 1,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,77; 6,32</t>
+          <t>3,79; 6,36</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,03</t>
+          <t>0,64; 2,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,16</t>
+          <t>1,68; 4,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,43</t>
+          <t>0,39; 2,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,32</t>
+          <t>1,37; 7,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 6,45</t>
+          <t>1,06; 5,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,55</t>
+          <t>1,62; 6,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 11,14</t>
+          <t>2,73; 10,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,4; 17,01</t>
+          <t>9,32; 17,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,95</t>
+          <t>1,0; 3,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,97</t>
+          <t>2,07; 4,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,6</t>
+          <t>1,2; 3,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 8,98</t>
+          <t>2,46; 8,84</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,59</t>
+          <t>1,13; 2,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,63</t>
+          <t>1,1; 2,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,81</t>
+          <t>1,23; 2,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 7,24</t>
+          <t>4,76; 7,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,51</t>
+          <t>1,42; 3,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,05</t>
+          <t>2,22; 4,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,6</t>
+          <t>2,07; 4,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,56</t>
+          <t>2,52; 6,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,69</t>
+          <t>1,43; 2,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,28</t>
+          <t>1,82; 3,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,18</t>
+          <t>1,76; 3,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,77; 6,32</t>
+          <t>3,57; 6,29</t>
         </is>
       </c>
     </row>
@@ -1277,52 +1277,52 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,23</t>
+          <t>1,11; 4,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,24</t>
+          <t>0,85; 3,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,8</t>
+          <t>1,98; 4,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,77</t>
+          <t>4,18; 7,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,52</t>
+          <t>1,07; 3,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,29; 7,88</t>
+          <t>4,59; 8,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,03; 7,68</t>
+          <t>4,17; 7,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,12; 16,7</t>
+          <t>10,48; 16,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,28</t>
+          <t>1,31; 3,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,73</t>
+          <t>3,34; 5,7</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,89; 12,91</t>
+          <t>9,16; 12,96</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,49</t>
+          <t>0,58; 3,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,98</t>
+          <t>2,73; 4,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,55; 8,84</t>
+          <t>5,58; 8,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,48; 7,59</t>
+          <t>4,49; 7,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,06; 14,87</t>
+          <t>10,99; 14,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,02</t>
+          <t>2,2; 3,96</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,47; 7,1</t>
+          <t>4,48; 7,1</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,64; 6,17</t>
+          <t>3,76; 6,2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,68; 11,73</t>
+          <t>8,62; 11,7</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,09; 1,95</t>
+          <t>1,12; 1,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,43</t>
+          <t>1,33; 2,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,13</t>
+          <t>1,23; 2,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,46; 5,28</t>
+          <t>3,61; 5,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,13</t>
+          <t>2,04; 3,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,25; 5,77</t>
+          <t>4,23; 5,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,67; 5,1</t>
+          <t>3,71; 5,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,44; 10,1</t>
+          <t>7,43; 10,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,44</t>
+          <t>1,72; 2,41</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,98; 3,93</t>
+          <t>2,94; 3,89</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 3,51</t>
+          <t>2,66; 3,5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,95; 7,62</t>
+          <t>5,89; 7,46</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2892; 14681</t>
+          <t>2870; 15519</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1003; 13516</t>
+          <t>1013; 12557</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2607; 14855</t>
+          <t>2996; 14109</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8319; 20397</t>
+          <t>8092; 20306</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2088; 11809</t>
+          <t>1978; 11905</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3115; 14623</t>
+          <t>3119; 15939</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2030; 11717</t>
+          <t>2077; 11657</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14593; 29906</t>
+          <t>14240; 29385</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6908; 21814</t>
+          <t>7107; 22240</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6050; 24161</t>
+          <t>5990; 22464</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6426; 20867</t>
+          <t>6122; 19447</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25019; 46152</t>
+          <t>25861; 45059</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>823; 7169</t>
+          <t>825; 8227</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3153; 18763</t>
+          <t>3224; 17238</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7635</t>
+          <t>0; 6322</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13775; 30161</t>
+          <t>13859; 30151</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6400</t>
+          <t>0; 6457</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3892; 15221</t>
+          <t>3948; 15212</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2092; 12437</t>
+          <t>2860; 13394</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14963; 28227</t>
+          <t>14927; 28606</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1742; 10311</t>
+          <t>1757; 10553</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9460; 27016</t>
+          <t>8291; 26863</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3141; 15807</t>
+          <t>2986; 13895</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31484; 52799</t>
+          <t>31607; 53131</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3388; 16432</t>
+          <t>3496; 14267</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10703; 32493</t>
+          <t>10591; 31061</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2365; 12701</t>
+          <t>2048; 12339</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8689; 48893</t>
+          <t>9183; 49780</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1898; 10815</t>
+          <t>1785; 9832</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4980; 17040</t>
+          <t>4220; 16650</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4444; 18513</t>
+          <t>4540; 17405</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15687; 28388</t>
+          <t>15549; 28822</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7147; 20920</t>
+          <t>7106; 22366</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18592; 44174</t>
+          <t>18441; 41340</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8298; 24772</t>
+          <t>8281; 24362</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21660; 74969</t>
+          <t>20552; 73847</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13968; 32045</t>
+          <t>14044; 32496</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12739; 30536</t>
+          <t>12768; 30039</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13812; 32334</t>
+          <t>14177; 32487</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48459; 74933</t>
+          <t>49284; 73865</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9586; 25097</t>
+          <t>10123; 25621</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17612; 38711</t>
+          <t>16988; 36899</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17590; 38018</t>
+          <t>17081; 37502</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22786; 64193</t>
+          <t>24602; 63964</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28651; 52450</t>
+          <t>27915; 52736</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35192; 63251</t>
+          <t>35099; 61936</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35440; 62868</t>
+          <t>34773; 63409</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>75902; 127203</t>
+          <t>71840; 126676</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3864; 14823</t>
+          <t>3890; 14603</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4403; 16552</t>
+          <t>4346; 17539</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12244; 29797</t>
+          <t>12283; 28790</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19893; 36912</t>
+          <t>19872; 36696</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6328; 20035</t>
+          <t>6100; 19997</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32634; 60024</t>
+          <t>34954; 61956</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29768; 56731</t>
+          <t>30775; 56987</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>85110; 140474</t>
+          <t>88188; 141906</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11898; 30130</t>
+          <t>12029; 29484</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42677; 72898</t>
+          <t>42471; 72549</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47404; 78444</t>
+          <t>47452; 78423</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>117010; 169921</t>
+          <t>120522; 170574</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1864</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1926</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5308</t>
+          <t>0; 6036</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1447; 8401</t>
+          <t>1387; 8096</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>35510; 62154</t>
+          <t>34040; 60616</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>61536; 98097</t>
+          <t>61951; 97233</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48458; 82100</t>
+          <t>48565; 82483</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>84206; 113184</t>
+          <t>83672; 110978</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>33555; 62178</t>
+          <t>33985; 61201</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>61515; 97678</t>
+          <t>61677; 97687</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49870; 84470</t>
+          <t>51417; 84908</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>86959; 117528</t>
+          <t>86330; 117226</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>35524; 63649</t>
+          <t>36510; 63511</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>46208; 83188</t>
+          <t>45406; 79910</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>43620; 72099</t>
+          <t>41697; 70986</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>116832; 178213</t>
+          <t>121876; 179439</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>70791; 105674</t>
+          <t>68943; 106280</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>151009; 204937</t>
+          <t>150147; 205507</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>129765; 180250</t>
+          <t>130859; 178281</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>266124; 361339</t>
+          <t>265691; 360498</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>115983; 161916</t>
+          <t>114070; 160359</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>207464; 274241</t>
+          <t>205162; 271261</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>181613; 242649</t>
+          <t>183723; 242144</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>413679; 529892</t>
+          <t>409606; 518621</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A_n_R3-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A_n_R3-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,28</t>
+          <t>0,62; 3,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,87</t>
+          <t>0,23; 3,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,29</t>
+          <t>0,6; 3,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,02</t>
+          <t>1,72; 4,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,88</t>
+          <t>0,64; 4,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,07</t>
+          <t>1,0; 4,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,36</t>
+          <t>0,57; 3,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 6,57</t>
+          <t>3,28; 6,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,85</t>
+          <t>0,87; 2,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,99</t>
+          <t>0,82; 3,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,51</t>
+          <t>0,81; 2,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,73</t>
+          <t>2,77; 4,86</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,24</t>
+          <t>0,22; 1,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,12</t>
+          <t>0,79; 4,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 6,67</t>
+          <t>2,88; 6,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,5</t>
+          <t>0,99; 4,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,6</t>
+          <t>0,61; 3,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,48</t>
+          <t>3,83; 7,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,43</t>
+          <t>0,13; 1,3</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,55</t>
+          <t>1,23; 3,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,85</t>
+          <t>0,43; 2,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,79; 6,36</t>
+          <t>3,75; 6,17</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,63</t>
+          <t>0,66; 2,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,93</t>
+          <t>1,66; 5,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,36</t>
+          <t>0,44; 2,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 7,45</t>
+          <t>4,53; 8,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 5,86</t>
+          <t>1,12; 6,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 6,4</t>
+          <t>1,62; 6,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 10,48</t>
+          <t>2,61; 10,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,32; 17,27</t>
+          <t>9,01; 16,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,15</t>
+          <t>0,99; 3,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,65</t>
+          <t>2,0; 4,78</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,54</t>
+          <t>1,23; 3,58</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,46; 8,84</t>
+          <t>6,42; 10,27</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,62</t>
+          <t>1,22; 2,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,59</t>
+          <t>1,08; 2,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,83</t>
+          <t>1,22; 2,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,76; 7,14</t>
+          <t>4,57; 6,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,59</t>
+          <t>1,37; 3,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,81</t>
+          <t>2,33; 5,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,54</t>
+          <t>2,08; 4,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,54</t>
+          <t>4,88; 7,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,7</t>
+          <t>1,42; 2,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,22</t>
+          <t>1,83; 3,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,21</t>
+          <t>1,76; 3,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 6,29</t>
+          <t>4,99; 6,7</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,17</t>
+          <t>1,23; 4,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,44</t>
+          <t>0,83; 3,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,64</t>
+          <t>2,11; 4,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,18; 7,72</t>
+          <t>3,65; 6,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,52</t>
+          <t>1,02; 3,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,59; 8,14</t>
+          <t>4,45; 8,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,17; 7,72</t>
+          <t>4,14; 7,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,48; 16,87</t>
+          <t>13,05; 16,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,21</t>
+          <t>1,36; 3,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,7</t>
+          <t>3,27; 5,72</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,49; 5,77</t>
+          <t>3,52; 5,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,16; 12,96</t>
+          <t>9,67; 12,37</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -1427,52 +1427,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,37</t>
+          <t>0,62; 3,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,85</t>
+          <t>2,67; 4,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,58; 8,76</t>
+          <t>5,67; 8,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,49; 7,62</t>
+          <t>4,65; 7,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,99; 14,58</t>
+          <t>10,96; 14,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,96</t>
+          <t>2,17; 3,88</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,48; 7,1</t>
+          <t>4,57; 7,17</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,76; 6,2</t>
+          <t>3,65; 6,27</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,62; 11,7</t>
+          <t>8,68; 11,67</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,94</t>
+          <t>1,1; 1,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,34</t>
+          <t>1,34; 2,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,1</t>
+          <t>1,26; 2,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,61; 5,32</t>
+          <t>4,13; 5,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,15</t>
+          <t>2,04; 3,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,23; 5,79</t>
+          <t>4,21; 5,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,71; 5,05</t>
+          <t>3,69; 5,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,43; 10,08</t>
+          <t>8,9; 10,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,41</t>
+          <t>1,71; 2,4</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,94; 3,89</t>
+          <t>2,99; 3,93</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,66; 3,5</t>
+          <t>2,65; 3,49</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,89; 7,46</t>
+          <t>6,77; 7,75</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>15031</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20786</t>
+          <t>23244</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34188</t>
+          <t>38275</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2870; 15519</t>
+          <t>2938; 16126</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1013; 12557</t>
+          <t>1022; 14179</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2996; 14109</t>
+          <t>2592; 14686</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8092; 20306</t>
+          <t>9483; 22015</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1978; 11905</t>
+          <t>1969; 13222</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3119; 15939</t>
+          <t>3146; 14975</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2077; 11657</t>
+          <t>1965; 11198</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14240; 29385</t>
+          <t>15998; 32645</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7107; 22240</t>
+          <t>6818; 22558</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5990; 22464</t>
+          <t>6135; 23438</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6122; 19447</t>
+          <t>6304; 21770</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25861; 45059</t>
+          <t>28799; 50513</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20563</t>
+          <t>21113</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20745</t>
+          <t>22471</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41308</t>
+          <t>43585</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>825; 8227</t>
+          <t>812; 7111</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3224; 17238</t>
+          <t>3315; 18837</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6322</t>
+          <t>0; 5933</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13859; 30151</t>
+          <t>13917; 29610</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6457</t>
+          <t>0; 6906</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3948; 15212</t>
+          <t>3353; 14778</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2860; 13394</t>
+          <t>2266; 12430</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14927; 28606</t>
+          <t>16216; 30991</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1757; 10553</t>
+          <t>976; 9575</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8291; 26863</t>
+          <t>9316; 26531</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2986; 13895</t>
+          <t>3246; 14979</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31607; 53131</t>
+          <t>33980; 55927</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27990</t>
+          <t>30337</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21042</t>
+          <t>23015</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49032</t>
+          <t>53352</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3496; 14267</t>
+          <t>3594; 15851</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10591; 31061</t>
+          <t>10458; 32281</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2048; 12339</t>
+          <t>2285; 12439</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9183; 49780</t>
+          <t>21350; 41608</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1785; 9832</t>
+          <t>1880; 10611</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4220; 16650</t>
+          <t>4206; 16744</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4540; 17405</t>
+          <t>4329; 17680</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15549; 28822</t>
+          <t>16890; 30710</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7106; 22366</t>
+          <t>7025; 22069</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18441; 41340</t>
+          <t>17833; 42499</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8281; 24362</t>
+          <t>8477; 24613</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20552; 73847</t>
+          <t>42315; 67690</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60042</t>
+          <t>64130</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>47020</t>
+          <t>51985</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>107062</t>
+          <t>116115</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14044; 32496</t>
+          <t>15107; 33771</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12768; 30039</t>
+          <t>12474; 30426</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14177; 32487</t>
+          <t>14074; 32253</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49284; 73865</t>
+          <t>51738; 78189</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10123; 25621</t>
+          <t>9789; 25298</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16988; 36899</t>
+          <t>17892; 39315</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17081; 37502</t>
+          <t>17195; 36574</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24602; 63964</t>
+          <t>42055; 64016</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27915; 52736</t>
+          <t>27745; 52314</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35099; 61936</t>
+          <t>35160; 62141</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>34773; 63409</t>
+          <t>34697; 61175</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>71840; 126676</t>
+          <t>99466; 133494</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27131</t>
+          <t>28613</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>117882</t>
+          <t>123820</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>145012</t>
+          <t>152432</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3890; 14603</t>
+          <t>4314; 15619</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4346; 17539</t>
+          <t>4239; 17082</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12283; 28790</t>
+          <t>13107; 29965</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19872; 36696</t>
+          <t>20716; 38774</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6100; 19997</t>
+          <t>5792; 20484</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34954; 61956</t>
+          <t>33926; 62415</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30775; 56987</t>
+          <t>30572; 56443</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>88188; 141906</t>
+          <t>108448; 139214</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12029; 29484</t>
+          <t>12532; 30419</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42471; 72549</t>
+          <t>41640; 72721</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47452; 78423</t>
+          <t>47836; 79162</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>120522; 170574</t>
+          <t>135267; 173031</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>97265</t>
+          <t>106478</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>100907</t>
+          <t>110112</t>
         </is>
       </c>
     </row>
@@ -2977,52 +2977,52 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6036</t>
+          <t>0; 6642</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1387; 8096</t>
+          <t>1460; 8192</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34040; 60616</t>
+          <t>33358; 60614</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>61951; 97233</t>
+          <t>62885; 98400</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48565; 82483</t>
+          <t>50339; 82266</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>83672; 110978</t>
+          <t>92514; 122297</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>33985; 61201</t>
+          <t>33590; 60041</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>61677; 97687</t>
+          <t>62836; 98708</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>51417; 84908</t>
+          <t>49957; 85861</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>86330; 117226</t>
+          <t>93923; 126183</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>152769</t>
+          <t>162858</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>324741</t>
+          <t>351011</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>477510</t>
+          <t>513870</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>36510; 63511</t>
+          <t>35839; 63752</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>45406; 79910</t>
+          <t>45750; 82537</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41697; 70986</t>
+          <t>42532; 72722</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>121876; 179439</t>
+          <t>142188; 186390</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>68943; 106280</t>
+          <t>68752; 107790</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>150147; 205507</t>
+          <t>149462; 203548</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>130859; 178281</t>
+          <t>130474; 182251</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>265691; 360498</t>
+          <t>323660; 378936</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>114070; 160359</t>
+          <t>113662; 159238</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>205162; 271261</t>
+          <t>208719; 273997</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>183723; 242144</t>
+          <t>183112; 241727</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>409606; 518621</t>
+          <t>479344; 548383</t>
         </is>
       </c>
     </row>
